--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 21/08/2026, 14:50</x:t>
+    <x:t>Conta: 4163084 | 25/08/2026, 19:23</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>38,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.003.598,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38,40%|Pós-Fixada</x:t>
+    <x:t>25,6%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.007.916,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,58 @@
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>61,5%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.008.443,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>33,3%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 6.513.321,42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,30%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>872.254,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.510.325,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.510.027,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.448,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.000.800,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.002.995,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.002.501,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41,0%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.018.629,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -118,10 +163,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>20/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 271,88</x:t>
+    <x:t>25/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,29</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -130,28 +175,25 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.002.066,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.112,10</x:t>
+    <x:t>R$ 2.005.067,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.942,56</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>19/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 44,76</x:t>
+    <x:t>R$ 44,82</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.500.783,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.024,29</x:t>
+    <x:t>R$ 1.502.900,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.449,59</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -163,49 +205,43 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.501.549,35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.084,05</x:t>
+    <x:t>R$ 1.503.084,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.478,13</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.439,63</x:t>
+    <x:t>R$ 1.441,09</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.003.092,53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.239,67</x:t>
+    <x:t>R$ 2.005.134,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.955,10</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,23</x:t>
+    <x:t>R$ 141,44</x:t>
   </x:si>
   <x:si>
     <x:t>7.087,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.000.952,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.029,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,08%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 9.800,75</x:t>
+    <x:t>R$ 1.002.441,74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.434,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,75</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -235,7 +271,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>9800,75</x:t>
+    <x:t>0,75</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -783,7 +819,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K24"/>
+  <x:dimension ref="A1:K30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -843,13 +879,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>13021843.2277658</x:v>
+        <x:v>19539868.1913983</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>13012042.4777658</x:v>
+        <x:v>19539867.4413983</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>9800.75</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1032,283 +1068,418 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="13"/>
+      <x:c r="B15" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
+      <x:c r="E15" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="F15" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13" t="s">
+      <x:c r="G15" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B15" s="13" t="s">
+      <x:c r="I15" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C15" s="13" t="s">
+      <x:c r="J15" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D15" s="13" t="s">
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="G16" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="I16" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
+      <x:c r="J16" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C16" s="13" t="s">
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="10" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B17" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H17" s="3"/>
-      <x:c r="I17" s="3"/>
-      <x:c r="J17" s="3"/>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B18" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D18" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E18" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F18" s="13" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G18" s="13" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A19" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B19" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C19" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E19" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F19" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G19" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4"/>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A21" s="8" t="s">
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="3"/>
+      <x:c r="J20" s="3"/>
+      <x:c r="K20" s="3"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H21" s="3"/>
+      <x:c r="I21" s="3"/>
+      <x:c r="J21" s="3"/>
+      <x:c r="K21" s="3"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A22" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H22" s="3"/>
+      <x:c r="I22" s="3"/>
+      <x:c r="J22" s="3"/>
+      <x:c r="K22" s="3"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A23" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
-      <x:c r="D21" s="9"/>
-      <x:c r="E21" s="9"/>
-      <x:c r="F21" s="9"/>
-      <x:c r="G21" s="9"/>
-      <x:c r="H21" s="9"/>
-      <x:c r="I21" s="9"/>
-      <x:c r="J21" s="9"/>
-      <x:c r="K21" s="10" t="s">
+      <x:c r="E23" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
         <x:v>63</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A23" s="11" t="s">
+      <x:c r="G23" s="13" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H23" s="3"/>
+      <x:c r="I23" s="3"/>
+      <x:c r="J23" s="3"/>
+      <x:c r="K23" s="3"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="13" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H24" s="3"/>
+      <x:c r="I24" s="3"/>
+      <x:c r="J24" s="3"/>
+      <x:c r="K24" s="3"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E25" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G25" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
+      <x:c r="K25" s="3"/>
+    </x:row>
+    <x:row r="26" spans="1:11">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A27" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="9"/>
+      <x:c r="D27" s="9"/>
+      <x:c r="E27" s="9"/>
+      <x:c r="F27" s="9"/>
+      <x:c r="G27" s="9"/>
+      <x:c r="H27" s="9"/>
+      <x:c r="I27" s="9"/>
+      <x:c r="J27" s="9"/>
+      <x:c r="K27" s="10" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="4"/>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="4"/>
+      <x:c r="G28" s="4"/>
+      <x:c r="H28" s="4"/>
+      <x:c r="I28" s="4"/>
+      <x:c r="J28" s="4"/>
+      <x:c r="K28" s="4"/>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A29" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B23" s="11" t="s">
+      <x:c r="B29" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D23" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H23" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="I23" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="J23" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="K23" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="12" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="I24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="J24" s="12" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="K24" s="12" t="s">
-        <x:v>74</x:v>
+      <x:c r="C29" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J29" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K29" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A30" s="12" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="I30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J30" s="12" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K30" s="12" t="s">
+        <x:v>86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="6">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A21:J21"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A27:J27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 25/08/2026, 19:23</x:t>
+    <x:t>Conta: 4163084 | 28/08/2026, 09:33</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>25,6%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.007.916,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,60%|Pós-Fixada</x:t>
+    <x:t>34,9%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.014.400,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,16 +94,16 @@
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>33,3%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 6.513.321,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33,30%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/08/2026</x:t>
+    <x:t>9,18%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.317.720,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,10%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>24/09/2026</x:t>
@@ -112,40 +112,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>872.254,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.510.325,52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.510.027,28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.448,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.000.800,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.002.995,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.002.501,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41,0%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.018.629,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>1.170,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.315.408,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.317.200,04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,9%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.028.991,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -163,10 +145,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>25/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,29</x:t>
+    <x:t>27/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,58</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -175,73 +157,79 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.005.067,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.942,56</x:t>
+    <x:t>R$ 2.007.193,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.001.672,49</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 44,82</x:t>
+    <x:t>26/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 44,87</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.502.900,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.449,59</x:t>
+    <x:t>R$ 1.504.647,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.972,55</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,98</x:t>
+    <x:t>R$ 1,99</x:t>
   </x:si>
   <x:si>
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.503.084,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.478,13</x:t>
+    <x:t>R$ 1.505.486,12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.275,52</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.441,09</x:t>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.443,31</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.005.134,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.955,10</x:t>
+    <x:t>R$ 2.008.223,21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.166,82</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,44</x:t>
+    <x:t>R$ 141,58</x:t>
   </x:si>
   <x:si>
     <x:t>7.087,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.002.441,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.434,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,75</x:t>
+    <x:t>R$ 1.003.440,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.781,62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 212,14</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -271,7 +259,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>0,75</x:t>
+    <x:t>212,14</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -819,7 +807,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K30"/>
+  <x:dimension ref="A1:K29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -879,13 +867,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>19539868.1913983</x:v>
+        <x:v>14361323.8306358</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>19539867.4413983</x:v>
+        <x:v>14361111.6906358</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0.75</x:v>
+        <x:v>212.14</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1097,127 +1085,125 @@
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13"/>
-      <x:c r="B15" s="13" t="s">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="s">
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
+      <x:c r="E15" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="F15" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="G15" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H15" s="13" t="s">
+      <x:c r="H15" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I15" s="13" t="s">
+      <x:c r="I15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="J15" s="13" t="s">
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E16" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G16" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H16" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I16" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10" t="s">
-        <x:v>42</x:v>
-      </x:c>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B20" s="11" t="s">
+      <x:c r="C20" s="13" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="D20" s="13" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="s">
+      <x:c r="E20" s="13" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="F20" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="G20" s="13" t="s">
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1226,19 +1212,19 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D21" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F21" s="13" t="s">
         <x:v>53</x:v>
@@ -1256,7 +1242,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
         <x:v>56</x:v>
@@ -1265,7 +1251,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="13" t="s">
         <x:v>58</x:v>
@@ -1283,22 +1269,22 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D23" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E23" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F23" s="13" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G23" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1306,170 +1292,143 @@
       <x:c r="K23" s="3"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C24" s="13" t="s">
+      <x:c r="A24" s="12" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D24" s="13" t="s">
+      <x:c r="B24" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
+      <x:c r="D24" s="12" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G24" s="13" t="s">
+      <x:c r="E24" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="s">
         <x:v>69</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
       <x:c r="J24" s="3"/>
       <x:c r="K24" s="3"/>
     </x:row>
-    <x:row r="25" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A25" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B25" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C25" s="12" t="s">
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A26" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
+      <x:c r="D26" s="9"/>
+      <x:c r="E26" s="9"/>
+      <x:c r="F26" s="9"/>
+      <x:c r="G26" s="9"/>
+      <x:c r="H26" s="9"/>
+      <x:c r="I26" s="9"/>
+      <x:c r="J26" s="9"/>
+      <x:c r="K26" s="10" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="s">
+    </x:row>
+    <x:row r="27" spans="1:11">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A28" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E25" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F25" s="12" t="s">
+      <x:c r="D28" s="11" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="s">
+      <x:c r="E28" s="11" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="H25" s="3"/>
-      <x:c r="I25" s="3"/>
-      <x:c r="J25" s="3"/>
-      <x:c r="K25" s="3"/>
-    </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="A26" s="4"/>
-      <x:c r="B26" s="4"/>
-      <x:c r="C26" s="4"/>
-      <x:c r="D26" s="4"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A27" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B27" s="9"/>
-      <x:c r="C27" s="9"/>
-      <x:c r="D27" s="9"/>
-      <x:c r="E27" s="9"/>
-      <x:c r="F27" s="9"/>
-      <x:c r="G27" s="9"/>
-      <x:c r="H27" s="9"/>
-      <x:c r="I27" s="9"/>
-      <x:c r="J27" s="9"/>
-      <x:c r="K27" s="10" t="s">
+      <x:c r="F28" s="11" t="s">
         <x:v>75</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11">
-      <x:c r="A28" s="4"/>
-      <x:c r="B28" s="4"/>
-      <x:c r="C28" s="4"/>
-      <x:c r="D28" s="4"/>
-      <x:c r="E28" s="4"/>
-      <x:c r="F28" s="4"/>
-      <x:c r="G28" s="4"/>
-      <x:c r="H28" s="4"/>
-      <x:c r="I28" s="4"/>
-      <x:c r="J28" s="4"/>
-      <x:c r="K28" s="4"/>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A29" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B29" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="s">
+      <x:c r="G28" s="11" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D29" s="11" t="s">
+      <x:c r="H28" s="11" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="s">
+      <x:c r="I28" s="11" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="s">
+      <x:c r="J28" s="11" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G29" s="11" t="s">
+      <x:c r="K28" s="11" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H29" s="11" t="s">
+    </x:row>
+    <x:row r="29" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A29" s="12" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="I29" s="11" t="s">
+      <x:c r="B29" s="12" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="J29" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K29" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A30" s="12" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="I30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J30" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K30" s="12" t="s">
-        <x:v>86</x:v>
+      <x:c r="C29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K29" s="12" t="s">
+        <x:v>82</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1478,8 +1437,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A18:F18"/>
-    <x:mergeCell ref="A27:J27"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A26:J26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 28/08/2026, 09:33</x:t>
+    <x:t>Conta: 4163084 | 31/08/2026, 17:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>34,9%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.014.400,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,90%|Pós-Fixada</x:t>
+    <x:t>21,9%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.016.563,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>9,18%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.317.720,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9,10%|Pós-Fixada</x:t>
+    <x:t>42,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 9.818.957,72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>24/08/2026</x:t>
@@ -118,16 +118,49 @@
     <x:t>R$ 1.315.408,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.317.200,04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,9%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.028.991,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,90%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.318.298,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.317.648,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>974.025,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.658,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.510,64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.069.767,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 6.999.999,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,1%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.035.401,05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -145,10 +178,7 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>27/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 272,58</x:t>
+    <x:t>R$ 272,86</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -157,28 +187,25 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.007.193,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.672,49</x:t>
+    <x:t>R$ 2.009.272,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.161,81</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>26/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 44,87</x:t>
+    <x:t>R$ 44,92</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.504.647,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.972,55</x:t>
+    <x:t>R$ 1.506.207,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.635,56</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -190,46 +217,43 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.505.486,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.275,52</x:t>
+    <x:t>R$ 1.506.214,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.637,55</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.443,31</x:t>
+    <x:t>R$ 1.444,03</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.008.223,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.166,82</x:t>
+    <x:t>R$ 2.009.222,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.145,03</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,58</x:t>
+    <x:t>R$ 141,72</x:t>
   </x:si>
   <x:si>
     <x:t>7.087,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.003.440,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.781,62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 212,14</x:t>
+    <x:t>R$ 1.004.484,33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.513,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 212,17</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -259,7 +283,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>212,14</x:t>
+    <x:t>212,17</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -807,7 +831,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K29"/>
+  <x:dimension ref="A1:K31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -867,13 +891,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>14361323.8306358</x:v>
+        <x:v>22871134.0028971</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>14361111.6906358</x:v>
+        <x:v>22870921.8328971</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>212.14</x:v>
+        <x:v>212.17</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1085,62 +1109,90 @@
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12" t="s">
+      <x:c r="A15" s="13"/>
+      <x:c r="B15" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="s">
+      <x:c r="E15" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="s">
+      <x:c r="F15" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="s">
+      <x:c r="G15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="s">
+      <x:c r="H15" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
+      <x:c r="I15" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="J15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10" t="s">
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13"/>
+      <x:c r="B16" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H17" s="3"/>
-      <x:c r="I17" s="3"/>
-      <x:c r="J17" s="3"/>
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C17" s="12"/>
+      <x:c r="D17" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G17" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I17" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="K17" s="3"/>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1151,86 +1203,62 @@
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="4"/>
       <x:c r="G18" s="4"/>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A19" s="8" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="10" t="s">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B20" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D20" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E20" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F20" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G20" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
+    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A21" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B21" s="13" t="s">
+      <x:c r="C21" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="D21" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="E21" s="11" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>54</x:v>
+      <x:c r="F21" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1239,25 +1267,25 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
+      <x:c r="E22" s="13" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D22" s="13" t="s">
+      <x:c r="F22" s="13" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
+      <x:c r="G22" s="13" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1266,25 +1294,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="s">
+      <x:c r="D23" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C23" s="13" t="s">
+      <x:c r="E23" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D23" s="13" t="s">
+      <x:c r="G23" s="13" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1292,61 +1320,85 @@
       <x:c r="K23" s="3"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="12" t="s">
+      <x:c r="A24" s="13" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B24" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C24" s="12" t="s">
+      <x:c r="E24" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="s">
+      <x:c r="G24" s="13" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="E24" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G24" s="12" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
       <x:c r="J24" s="3"/>
       <x:c r="K24" s="3"/>
     </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A26" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
-      <x:c r="D26" s="9"/>
-      <x:c r="E26" s="9"/>
-      <x:c r="F26" s="9"/>
-      <x:c r="G26" s="9"/>
-      <x:c r="H26" s="9"/>
-      <x:c r="I26" s="9"/>
-      <x:c r="J26" s="9"/>
-      <x:c r="K26" s="10" t="s">
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="s">
         <x:v>71</x:v>
       </x:c>
+      <x:c r="E25" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
+      <x:c r="K25" s="3"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H26" s="3"/>
+      <x:c r="I26" s="3"/>
+      <x:c r="J26" s="3"/>
+      <x:c r="K26" s="3"/>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="4"/>
@@ -1361,74 +1413,104 @@
       <x:c r="J27" s="4"/>
       <x:c r="K27" s="4"/>
     </x:row>
-    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A28" s="11" t="s">
+    <x:row r="28" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A28" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="D28" s="9"/>
+      <x:c r="E28" s="9"/>
+      <x:c r="F28" s="9"/>
+      <x:c r="G28" s="9"/>
+      <x:c r="H28" s="9"/>
+      <x:c r="I28" s="9"/>
+      <x:c r="J28" s="9"/>
+      <x:c r="K28" s="10" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="4"/>
+      <x:c r="I29" s="4"/>
+      <x:c r="J29" s="4"/>
+      <x:c r="K29" s="4"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A30" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B28" s="11" t="s">
+      <x:c r="B30" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="I28" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="K28" s="11" t="s">
+      <x:c r="C30" s="11" t="s">
         <x:v>80</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A29" s="12" t="s">
+      <x:c r="D30" s="11" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B29" s="12" t="s">
+      <x:c r="E30" s="11" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="I29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="J29" s="12" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="K29" s="12" t="s">
-        <x:v>82</x:v>
+      <x:c r="F30" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K30" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A31" s="12" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J31" s="12" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K31" s="12" t="s">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1437,8 +1519,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A26:J26"/>
+    <x:mergeCell ref="A19:F19"/>
+    <x:mergeCell ref="A28:J28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 31/08/2026, 17:49</x:t>
+    <x:t>Conta: 4163084 | 01/09/2026, 15:58</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>21,9%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.016.563,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21,90%|Pós-Fixada</x:t>
+    <x:t>29,7%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.018.727,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>42,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 9.818.957,72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,90%|Pós-Fixada</x:t>
+    <x:t>22,6%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.822.675,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,60%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>24/08/2026</x:t>
@@ -118,10 +118,10 @@
     <x:t>R$ 1.315.408,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.318.298,86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.317.648,48</x:t>
+    <x:t>R$ 1.318.877,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.318.097,10</x:t>
   </x:si>
   <x:si>
     <x:t>28/08/2026</x:t>
@@ -130,16 +130,16 @@
     <x:t>29/09/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>974.025,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.658,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.500.510,64</x:t>
+    <x:t>974.024,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.499.998,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.316,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.501.020,14</x:t>
   </x:si>
   <x:si>
     <x:t>31/08/2026</x:t>
@@ -148,19 +148,25 @@
     <x:t>01/10/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>4.069.767,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 6.999.999,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35,1%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.035.401,05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35,10%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>582.582,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.041,14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.481,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.382,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.039.441,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -178,7 +184,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 272,86</x:t>
+    <x:t>01/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,00</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -187,25 +196,25 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.009.272,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.161,81</x:t>
+    <x:t>R$ 2.010.298,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.751,06</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 44,92</x:t>
+    <x:t>R$ 44,94</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.506.207,01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.635,56</x:t>
+    <x:t>R$ 1.506.937,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.502.365,79</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -217,43 +226,43 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.506.214,61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.637,55</x:t>
+    <x:t>R$ 1.506.981,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.502.380,61</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.444,03</x:t>
+    <x:t>R$ 1.444,78</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.009.222,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.145,03</x:t>
+    <x:t>R$ 2.010.261,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.003.737,70</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,72</x:t>
+    <x:t>R$ 141,79</x:t>
   </x:si>
   <x:si>
     <x:t>7.087,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.484,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.513,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 212,17</x:t>
+    <x:t>R$ 1.004.963,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.792,59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 213,69</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -283,7 +292,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>212,17</x:t>
+    <x:t>213,69</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -891,13 +900,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>22871134.0028971</x:v>
+        <x:v>16881057.8533493</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>22870921.8328971</x:v>
+        <x:v>16880844.1633493</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>212.17</x:v>
+        <x:v>213.69</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1188,10 +1197,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K17" s="3"/>
     </x:row>
@@ -1210,7 +1219,7 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="45" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
@@ -1218,7 +1227,7 @@
       <x:c r="E19" s="9"/>
       <x:c r="F19" s="9"/>
       <x:c r="G19" s="10" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1240,19 +1249,19 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A21" s="11" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C21" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D21" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E21" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F21" s="11" t="s">
         <x:v>16</x:v>
@@ -1267,25 +1276,25 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F22" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G22" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1294,25 +1303,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="F23" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G23" s="13" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1321,25 +1330,25 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="13" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F24" s="13" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1348,25 +1357,25 @@
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
       <x:c r="A25" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C25" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D25" s="13" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E25" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F25" s="13" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G25" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
@@ -1375,25 +1384,25 @@
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C26" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G26" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H26" s="3"/>
       <x:c r="I26" s="3"/>
@@ -1427,7 +1436,7 @@
       <x:c r="I28" s="9"/>
       <x:c r="J28" s="9"/>
       <x:c r="K28" s="10" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1451,66 +1460,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="11" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D30" s="11" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E30" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F30" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G30" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H30" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I30" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J30" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K30" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11" ht="30" customHeight="1">
       <x:c r="A31" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K31" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 01/09/2026, 15:58</x:t>
+    <x:t>Conta: 4163084 | 04/09/2026, 14:15</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>29,7%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.018.727,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29,70%|Pós-Fixada</x:t>
+    <x:t>37,5%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.025.224,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,79 +94,40 @@
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>22,6%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.822.675,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22,60%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/09/2026</x:t>
+    <x:t>2,42%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 324.338,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,40%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/10/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.170,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.315.408,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.318.877,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.318.097,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>974.024,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.499.998,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.316,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.501.020,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>582.582,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.041,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.481,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.382,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.039.441,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47,60%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>188.238,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 323.769,39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 324.210,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60,1%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.052.262,18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -184,10 +145,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>01/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,00</x:t>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,42</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -196,25 +157,28 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.010.298,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.751,06</x:t>
+    <x:t>R$ 2.013.361,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.902,41</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 44,94</x:t>
+    <x:t>03/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 45,01</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.506.937,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.502.365,79</x:t>
+    <x:t>R$ 1.509.350,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.503.913,27</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -226,43 +190,43 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.506.981,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.502.380,61</x:t>
+    <x:t>R$ 1.509.666,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.504.045,40</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.444,78</x:t>
+    <x:t>R$ 1.447,05</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.010.261,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.003.737,70</x:t>
+    <x:t>R$ 2.013.430,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.005.932,71</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,79</x:t>
+    <x:t>R$ 142,00</x:t>
   </x:si>
   <x:si>
     <x:t>7.087,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.963,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.792,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 213,69</x:t>
+    <x:t>R$ 1.006.453,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.837,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 214,85</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -292,7 +256,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>213,69</x:t>
+    <x:t>214,85</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -840,7 +804,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K31"/>
+  <x:dimension ref="A1:K29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -900,13 +864,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>16881057.8533493</x:v>
+        <x:v>13402039.9455079</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>16880844.1633493</x:v>
+        <x:v>13401825.0955079</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>213.69</x:v>
+        <x:v>214.85</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1118,90 +1082,62 @@
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13"/>
-      <x:c r="B15" s="13" t="s">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="s">
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
+      <x:c r="E15" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="F15" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="G15" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H15" s="13" t="s">
+      <x:c r="H15" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I15" s="13" t="s">
+      <x:c r="I15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="J15" s="13" t="s">
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13"/>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="13"/>
-      <x:c r="D16" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="12"/>
-      <x:c r="B17" s="12" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C17" s="12"/>
-      <x:c r="D17" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G17" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H17" s="12" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I17" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
       <x:c r="K17" s="3"/>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1212,62 +1148,86 @@
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="4"/>
       <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A19" s="8" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="10" t="s">
-        <x:v>49</x:v>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A21" s="11" t="s">
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="s">
+      <x:c r="C21" s="13" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="D21" s="13" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="s">
+      <x:c r="E21" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="G21" s="13" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1279,22 +1239,22 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C22" s="13" t="s">
+      <x:c r="D22" s="13" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D22" s="13" t="s">
+      <x:c r="E22" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E22" s="13" t="s">
+      <x:c r="G22" s="13" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1303,25 +1263,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
+      <x:c r="E23" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D23" s="13" t="s">
+      <x:c r="G23" s="13" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1329,85 +1289,61 @@
       <x:c r="K23" s="3"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
+      <x:c r="A24" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="13" t="s">
+      <x:c r="E24" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D24" s="13" t="s">
+      <x:c r="G24" s="12" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G24" s="13" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
       <x:c r="J24" s="3"/>
       <x:c r="K24" s="3"/>
     </x:row>
-    <x:row r="25" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A25" s="13" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B25" s="13" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C25" s="13" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D25" s="13" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E25" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F25" s="13" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G25" s="13" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H25" s="3"/>
-      <x:c r="I25" s="3"/>
-      <x:c r="J25" s="3"/>
-      <x:c r="K25" s="3"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A26" s="12" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B26" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C26" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D26" s="12" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E26" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F26" s="12" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G26" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H26" s="3"/>
-      <x:c r="I26" s="3"/>
-      <x:c r="J26" s="3"/>
-      <x:c r="K26" s="3"/>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A26" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
+      <x:c r="D26" s="9"/>
+      <x:c r="E26" s="9"/>
+      <x:c r="F26" s="9"/>
+      <x:c r="G26" s="9"/>
+      <x:c r="H26" s="9"/>
+      <x:c r="I26" s="9"/>
+      <x:c r="J26" s="9"/>
+      <x:c r="K26" s="10" t="s">
+        <x:v>70</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="4"/>
@@ -1422,104 +1358,74 @@
       <x:c r="J27" s="4"/>
       <x:c r="K27" s="4"/>
     </x:row>
-    <x:row r="28" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A28" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B28" s="9"/>
-      <x:c r="C28" s="9"/>
-      <x:c r="D28" s="9"/>
-      <x:c r="E28" s="9"/>
-      <x:c r="F28" s="9"/>
-      <x:c r="G28" s="9"/>
-      <x:c r="H28" s="9"/>
-      <x:c r="I28" s="9"/>
-      <x:c r="J28" s="9"/>
-      <x:c r="K28" s="10" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11">
-      <x:c r="A29" s="4"/>
-      <x:c r="B29" s="4"/>
-      <x:c r="C29" s="4"/>
-      <x:c r="D29" s="4"/>
-      <x:c r="E29" s="4"/>
-      <x:c r="F29" s="4"/>
-      <x:c r="G29" s="4"/>
-      <x:c r="H29" s="4"/>
-      <x:c r="I29" s="4"/>
-      <x:c r="J29" s="4"/>
-      <x:c r="K29" s="4"/>
-    </x:row>
-    <x:row r="30" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A30" s="11" t="s">
+    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A28" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B30" s="11" t="s">
+      <x:c r="B28" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="I30" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="K30" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A31" s="12" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="G31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J31" s="12" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K31" s="12" t="s">
-        <x:v>93</x:v>
+      <x:c r="C28" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K28" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A29" s="12" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K29" s="12" t="s">
+        <x:v>81</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1528,8 +1434,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A19:F19"/>
-    <x:mergeCell ref="A28:J28"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A26:J26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 04/09/2026, 14:15</x:t>
+    <x:t>Conta: 4163084 | 10/09/2026, 14:05</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>37,5%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.025.224,47</x:t>
+    <x:t>R$ 5.031.730,33</x:t>
   </x:si>
   <x:si>
     <x:t>37,40%|Pós-Fixada</x:t>
@@ -97,7 +97,7 @@
     <x:t>2,42%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 324.338,45</x:t>
+    <x:t>R$ 324.765,90</x:t>
   </x:si>
   <x:si>
     <x:t>2,40%|Pós-Fixada</x:t>
@@ -118,13 +118,13 @@
     <x:t>R$ 323.769,39</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 324.210,41</x:t>
+    <x:t>R$ 324.541,69</x:t>
   </x:si>
   <x:si>
     <x:t>60,1%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 8.052.262,18</x:t>
+    <x:t>R$ 8.065.980,56</x:t>
   </x:si>
   <x:si>
     <x:t>60,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
@@ -145,10 +145,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,42</x:t>
+    <x:t>10/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 273,83</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -157,73 +157,73 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.013.361,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.902,41</x:t>
+    <x:t>R$ 2.016.406,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.009.790,46</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>03/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 45,01</x:t>
+    <x:t>09/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 45,13</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.509.350,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.503.913,27</x:t>
+    <x:t>R$ 1.513.404,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.507.687,56</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1,99</x:t>
+    <x:t>R$ 2,00</x:t>
   </x:si>
   <x:si>
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.509.666,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.504.045,40</x:t>
+    <x:t>R$ 1.511.812,65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.506.774,56</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.447,05</x:t>
+    <x:t>R$ 1.449,20</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.013.430,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.005.932,71</x:t>
+    <x:t>R$ 2.016.420,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.009.798,73</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 142,00</x:t>
+    <x:t>R$ 142,21</x:t>
   </x:si>
   <x:si>
     <x:t>7.087,60</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.006.453,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.837,53</x:t>
+    <x:t>R$ 1.007.936,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.004.726,66</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 214,85</x:t>
@@ -864,10 +864,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>13402039.9455079</x:v>
+        <x:v>13422691.6375945</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>13401825.0955079</x:v>
+        <x:v>13422476.7875945</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>214.85</x:v>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 10/09/2026, 14:05</x:t>
+    <x:t>Conta: 4163084 | 16/09/2026, 08:42</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>37,5%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.031.730,33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37,40%|Pós-Fixada</x:t>
+    <x:t>54,8%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.686.972,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -85,49 +85,22 @@
     <x:t>83,50% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>432,00</x:t>
+    <x:t>316,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.997.129,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,42%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 324.765,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,40%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>188.238,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 323.769,39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 324.541,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60,1%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.065.980,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 3.655.307,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,0%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.028.538,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -142,43 +115,25 @@
     <x:t>Em cotização</x:t>
   </x:si>
   <x:si>
-    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 273,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.363,69</x:t>
+    <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 45,16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.016.406,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.009.790,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 45,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33.531,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.513.404,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.507.687,56</x:t>
+    <x:t>R$ 1.514.304,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.977,71</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -190,43 +145,16 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.511.812,65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.506.774,56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.449,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.391,40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.016.420,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.009.798,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 142,21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.087,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.007.936,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.004.726,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 214,85</x:t>
+    <x:t>R$ 1.514.233,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.509.927,85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,16%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 11.068,32</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -256,7 +184,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>214,85</x:t>
+    <x:t>11068,32</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -804,7 +732,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K29"/>
+  <x:dimension ref="A1:K21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -864,13 +792,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>13422691.6375945</x:v>
+        <x:v>6726579.0960094</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>13422476.7875945</x:v>
+        <x:v>6715510.7760094</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>214.85</x:v>
+        <x:v>11068.32</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1053,389 +981,202 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H15" s="3"/>
+      <x:c r="I15" s="3"/>
+      <x:c r="J15" s="3"/>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="9"/>
+      <x:c r="H18" s="9"/>
+      <x:c r="I18" s="9"/>
+      <x:c r="J18" s="9"/>
+      <x:c r="K18" s="10" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
+      <x:c r="H19" s="4"/>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="4"/>
+      <x:c r="K19" s="4"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H17" s="3"/>
-      <x:c r="I17" s="3"/>
-      <x:c r="J17" s="3"/>
-      <x:c r="K17" s="3"/>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H19" s="3"/>
-      <x:c r="I19" s="3"/>
-      <x:c r="J19" s="3"/>
-      <x:c r="K19" s="3"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B20" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D20" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E20" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F20" s="13" t="s">
+      <x:c r="C20" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G20" s="13" t="s">
+      <x:c r="D20" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H20" s="3"/>
-      <x:c r="I20" s="3"/>
-      <x:c r="J20" s="3"/>
-      <x:c r="K20" s="3"/>
+      <x:c r="E20" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K20" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C21" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D21" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H21" s="3"/>
-      <x:c r="I21" s="3"/>
-      <x:c r="J21" s="3"/>
-      <x:c r="K21" s="3"/>
-    </x:row>
-    <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
+      <x:c r="A21" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D22" s="13" t="s">
+      <x:c r="B21" s="12" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H22" s="3"/>
-      <x:c r="I22" s="3"/>
-      <x:c r="J22" s="3"/>
-      <x:c r="K22" s="3"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H23" s="3"/>
-      <x:c r="I23" s="3"/>
-      <x:c r="J23" s="3"/>
-      <x:c r="K23" s="3"/>
-    </x:row>
-    <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B24" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C24" s="12" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E24" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G24" s="12" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H24" s="3"/>
-      <x:c r="I24" s="3"/>
-      <x:c r="J24" s="3"/>
-      <x:c r="K24" s="3"/>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A26" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
-      <x:c r="D26" s="9"/>
-      <x:c r="E26" s="9"/>
-      <x:c r="F26" s="9"/>
-      <x:c r="G26" s="9"/>
-      <x:c r="H26" s="9"/>
-      <x:c r="I26" s="9"/>
-      <x:c r="J26" s="9"/>
-      <x:c r="K26" s="10" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:11">
-      <x:c r="A27" s="4"/>
-      <x:c r="B27" s="4"/>
-      <x:c r="C27" s="4"/>
-      <x:c r="D27" s="4"/>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
-      <x:c r="H27" s="4"/>
-      <x:c r="I27" s="4"/>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A28" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B28" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I28" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="K28" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A29" s="12" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="J29" s="12" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K29" s="12" t="s">
-        <x:v>81</x:v>
+      <x:c r="C21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K21" s="12" t="s">
+        <x:v>57</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A26:J26"/>
+    <x:mergeCell ref="A18:J18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 16/09/2026, 08:42</x:t>
+    <x:t>Conta: 4163084 | 21/09/2026, 16:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>54,8%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.686.972,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54,80%|Pós-Fixada</x:t>
+    <x:t>36,0%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.705.655,13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -85,22 +85,22 @@
     <x:t>83,50% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>316,00</x:t>
+    <x:t>146,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.655.307,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,0%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.028.538,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>R$ 1.688.844,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64,0%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.034.792,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -118,10 +118,10 @@
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
-    <x:t>14/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 45,16</x:t>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 45,25</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
@@ -130,10 +130,10 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.514.304,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.977,71</x:t>
+    <x:t>R$ 1.517.194,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.513.325,47</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -145,16 +145,16 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.514.233,46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.509.927,85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,16%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 11.068,32</x:t>
+    <x:t>R$ 1.517.598,58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.513.638,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 659,81</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -184,7 +184,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>11068,32</x:t>
+    <x:t>659,81</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -792,13 +792,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>6726579.0960094</x:v>
+        <x:v>4741107.67470826</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6715510.7760094</x:v>
+        <x:v>4740447.86470826</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>11068.32</x:v>
+        <x:v>659.81</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 21/09/2026, 16:40</x:t>
+    <x:t>Conta: 4163084 | 23/09/2026, 09:36</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>36,0%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.705.655,13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35,90%|Pós-Fixada</x:t>
+    <x:t>14,5%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.707.102,11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,50%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,67 +94,37 @@
     <x:t>R$ 1.688.844,68</x:t>
   </x:si>
   <x:si>
-    <x:t>64,0%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.034.792,73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor cota</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qtd. cotas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Em cotização</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 45,25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33.531,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.517.194,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.513.325,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>757.260,27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.517.598,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.513.638,90</x:t>
+    <x:t>85,5%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 10.032.329,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,40%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.306.918,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 10.028.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 10.031.355,03</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 659,81</x:t>
+    <x:t>R$ 664,30</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -184,7 +154,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>659,81</x:t>
+    <x:t>664,3</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -380,7 +350,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -430,10 +400,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -732,10 +698,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K21"/>
+  <x:dimension ref="A1:K20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -792,13 +758,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4741107.67470826</x:v>
+        <x:v>11740095.4761668</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4740447.86470826</x:v>
+        <x:v>11739431.1761668</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>659.81</x:v>
+        <x:v>664.3</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -981,193 +947,174 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
+      <x:c r="E15" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="F15" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13" t="s">
+      <x:c r="G15" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B15" s="13" t="s">
+      <x:c r="I15" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C15" s="13" t="s">
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D15" s="13" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="9"/>
+      <x:c r="H17" s="9"/>
+      <x:c r="I17" s="9"/>
+      <x:c r="J17" s="9"/>
+      <x:c r="K17" s="10" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="D19" s="11" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="E19" s="11" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12" t="s">
+      <x:c r="F19" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B16" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="12" t="s">
+      <x:c r="G19" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="H19" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="s">
+      <x:c r="I19" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="s">
+      <x:c r="J19" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
+      <x:c r="K19" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="9"/>
-      <x:c r="H18" s="9"/>
-      <x:c r="I18" s="9"/>
-      <x:c r="J18" s="9"/>
-      <x:c r="K18" s="10" t="s">
+    </x:row>
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="12" t="s">
         <x:v>46</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
-      <x:c r="H19" s="4"/>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="B20" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I20" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="J20" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K20" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J21" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K21" s="12" t="s">
-        <x:v>57</x:v>
+      <x:c r="C20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K20" s="12" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1176,7 +1123,7 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A18:J18"/>
+    <x:mergeCell ref="A17:J17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 23/09/2026, 09:36</x:t>
+    <x:t>Conta: 4163084 | 30/09/2026, 08:51</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>14,5%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.707.102,11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,50%|Pós-Fixada</x:t>
+    <x:t>20,7%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.710.724,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.688.844,68</x:t>
   </x:si>
   <x:si>
-    <x:t>85,5%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 10.032.329,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,40%|Pós-Fixada</x:t>
+    <x:t>79,3%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 6.550.499,68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>22/09/2026</x:t>
@@ -112,19 +112,40 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>6.306.918,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 10.028.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 10.031.355,03</x:t>
+    <x:t>3.481.039,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.534.852,22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.549.204,02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.545.974,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/10/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>564.971,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.295,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.001.004,14</x:t>
   </x:si>
   <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 664,30</x:t>
+    <x:t>R$ 665,44</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -154,7 +175,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>664,3</x:t>
+    <x:t>665,44</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -350,7 +371,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -400,6 +421,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -698,7 +723,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K20"/>
+  <x:dimension ref="A1:K21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -758,13 +783,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>11740095.4761668</x:v>
+        <x:v>8261890.03573688</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>11739431.1761668</x:v>
+        <x:v>8261224.59573688</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>664.3</x:v>
+        <x:v>665.44</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -976,145 +1001,174 @@
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12" t="s">
+      <x:c r="A15" s="13"/>
+      <x:c r="B15" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="s">
+      <x:c r="E15" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="s">
+      <x:c r="F15" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="s">
+      <x:c r="G15" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="s">
+      <x:c r="H15" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
+      <x:c r="I15" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
+      <x:c r="J15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="9"/>
-      <x:c r="H17" s="9"/>
-      <x:c r="I17" s="9"/>
-      <x:c r="J17" s="9"/>
-      <x:c r="K17" s="10" t="s">
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="9"/>
+      <x:c r="H18" s="9"/>
+      <x:c r="I18" s="9"/>
+      <x:c r="J18" s="9"/>
+      <x:c r="K18" s="10" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
+      <x:c r="H19" s="4"/>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="4"/>
+      <x:c r="K19" s="4"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B20" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H19" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I19" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J19" s="11" t="s">
+      <x:c r="C20" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="K19" s="11" t="s">
+      <x:c r="D20" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="12" t="s">
+      <x:c r="E20" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B20" s="12" t="s">
+      <x:c r="F20" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J20" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K20" s="12" t="s">
-        <x:v>47</x:v>
+      <x:c r="G20" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K20" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K21" s="12" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1123,7 +1177,7 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A17:J17"/>
+    <x:mergeCell ref="A18:J18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 30/09/2026, 08:51</x:t>
+    <x:t>Conta: 4163084 | 13/10/2026, 11:11</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>20,7%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.710.724,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,70%|Pós-Fixada</x:t>
+    <x:t>24,2%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.716.537,41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.688.844,68</x:t>
   </x:si>
   <x:si>
-    <x:t>79,3%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 6.550.499,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79,20%|Pós-Fixada</x:t>
+    <x:t>75,8%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.368.118,29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75,70%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>22/09/2026</x:t>
@@ -112,16 +112,16 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>3.481.039,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.534.852,22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.549.204,02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.545.974,86</x:t>
+    <x:t>2.727.719,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.337.073,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.363.359,34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.357.445,00</x:t>
   </x:si>
   <x:si>
     <x:t>25/09/2026</x:t>
@@ -136,16 +136,13 @@
     <x:t>R$ 1.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.001.295,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.001.004,14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 665,44</x:t>
+    <x:t>R$ 1.004.758,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.003.688,19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 245,74</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -175,7 +172,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>665,44</x:t>
+    <x:t>245,74</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -783,13 +780,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>8261890.03573688</x:v>
+        <x:v>7084901.4408449</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>8261224.59573688</x:v>
+        <x:v>7084655.7008449</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>665.44</x:v>
+        <x:v>245.74</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1073,7 +1070,7 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="45" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1085,7 +1082,7 @@
       <x:c r="I18" s="9"/>
       <x:c r="J18" s="9"/>
       <x:c r="K18" s="10" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1109,66 +1106,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="s">
+      <x:c r="E20" s="11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="F20" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="G20" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="H20" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H20" s="11" t="s">
+      <x:c r="I20" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="I20" s="11" t="s">
+      <x:c r="J20" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J20" s="11" t="s">
+      <x:c r="K20" s="11" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="K20" s="11" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="C21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 13/10/2026, 11:11</x:t>
+    <x:t>Conta: 4163084 | 14/10/2026, 08:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>24,2%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.716.537,41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24,20%|Pós-Fixada</x:t>
+    <x:t>26,9%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.717.265,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,80%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,13 +94,13 @@
     <x:t>R$ 1.688.844,68</x:t>
   </x:si>
   <x:si>
-    <x:t>75,8%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.368.118,29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75,70%|Pós-Fixada</x:t>
+    <x:t>73,1%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.669.181,90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73,00%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>22/09/2026</x:t>
@@ -112,16 +112,16 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>2.727.719,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.337.073,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.363.359,34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.357.445,00</x:t>
+    <x:t>2.289.525,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.640.344,89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.663.989,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.658.669,23</x:t>
   </x:si>
   <x:si>
     <x:t>25/09/2026</x:t>
@@ -136,13 +136,16 @@
     <x:t>R$ 1.000.000,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.004.758,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.003.688,19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 245,74</x:t>
+    <x:t>R$ 1.005.192,70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.004.024,34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,02%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.553,55</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -172,10 +175,13 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>245,74</x:t>
+    <x:t>246,83</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1306,72</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -780,16 +786,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>7084901.4408449</x:v>
+        <x:v>6388000.81393208</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>7084655.7008449</x:v>
+        <x:v>6386447.26393208</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>245.74</x:v>
+        <x:v>246.83</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>0</x:v>
+        <x:v>1306.72</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -1070,7 +1076,7 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="45" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
@@ -1082,7 +1088,7 @@
       <x:c r="I18" s="9"/>
       <x:c r="J18" s="9"/>
       <x:c r="K18" s="10" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1106,66 +1112,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="11" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D20" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E20" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F20" s="11" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G20" s="11" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H20" s="11" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I20" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J20" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K20" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 14/10/2026, 08:49</x:t>
+    <x:t>Conta: 4163084 | 27/10/2026, 19:00</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>26,9%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.717.265,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26,80%|Pós-Fixada</x:t>
+    <x:t>99,3%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.582.146,08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,30%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -85,67 +85,19 @@
     <x:t>83,50% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>146,00</x:t>
+    <x:t>134,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.688.844,68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73,1%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.669.181,90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73,00%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.289.525,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.640.344,89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.663.989,20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.658.669,23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29/10/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>564.971,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.005.192,70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.004.024,34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,02%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.553,55</x:t>
+    <x:t>R$ 1.550.035,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,68%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 10.757,78</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -175,13 +127,10 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>246,83</x:t>
+    <x:t>10757,78</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1306,72</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -374,7 +323,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -424,10 +373,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -726,7 +671,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K21"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -786,16 +731,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>6388000.81393208</x:v>
+        <x:v>1592903.86332488</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>6386447.26393208</x:v>
+        <x:v>1582146.08332488</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>246.83</x:v>
+        <x:v>10757.78</x:v>
       </x:c>
       <x:c r="D4" s="7">
-        <x:v>1306.72</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
@@ -949,13 +894,13 @@
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
-      <x:c r="G12" s="10" t="s">
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="10" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H12" s="3"/>
-      <x:c r="I12" s="3"/>
-      <x:c r="J12" s="3"/>
-      <x:c r="K12" s="3"/>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="4"/>
@@ -965,222 +910,87 @@
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4"/>
-      <x:c r="H13" s="3"/>
-      <x:c r="I13" s="3"/>
-      <x:c r="J13" s="3"/>
-      <x:c r="K13" s="3"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A14" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B14" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D14" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E14" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F14" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G14" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H14" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I14" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J14" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K14" s="3"/>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13"/>
-      <x:c r="B15" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E15" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F15" s="13" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H15" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I15" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="J15" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="12"/>
-      <x:c r="B16" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="A15" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="s">
+      <x:c r="B15" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H16" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I16" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="9"/>
-      <x:c r="H18" s="9"/>
-      <x:c r="I18" s="9"/>
-      <x:c r="J18" s="9"/>
-      <x:c r="K18" s="10" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
-      <x:c r="H19" s="4"/>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
-    </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="I20" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J20" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K20" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H21" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="I21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J21" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K21" s="12" t="s">
-        <x:v>54</x:v>
+      <x:c r="C15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A18:J18"/>
+    <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 27/10/2026, 19:00</x:t>
+    <x:t>Conta: 4163084 | 29/10/2026, 16:11</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>99,3%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.582.146,08</x:t>
+    <x:t>R$ 1.583.488,28</x:t>
   </x:si>
   <x:si>
     <x:t>99,30%|Pós-Fixada</x:t>
@@ -94,7 +94,7 @@
     <x:t>R$ 1.550.035,53</x:t>
   </x:si>
   <x:si>
-    <x:t>0,68%|Saldo projetado</x:t>
+    <x:t>0,67%|Saldo projetado</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 10.757,78</x:t>
@@ -731,10 +731,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1592903.86332488</x:v>
+        <x:v>1594246.06025354</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1582146.08332488</x:v>
+        <x:v>1583488.28025354</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>10757.78</x:v>
